--- a/Employee Attendance Tracker.xlsx
+++ b/Employee Attendance Tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\p2 excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1DFD9A3-F695-419E-9666-51D83A8FD78B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B136A3-2095-4E7A-999C-8EACA375082B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{337F30DB-46CA-4179-868E-2E5CFE2A735B}"/>
   </bookViews>
@@ -805,22 +805,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>1</c:v>
@@ -2133,8 +2133,8 @@
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>320040</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
@@ -2846,8 +2846,8 @@
         <v>11</v>
       </c>
       <c r="I2">
-        <f>COUNTIF(H2:H9, "Absent")</f>
-        <v>2</v>
+        <f>COUNTIFS($A$2:$A$100, A2, $H$2:$H$100, "Absent")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -2876,8 +2876,8 @@
         <v>15</v>
       </c>
       <c r="I3">
-        <f t="shared" ref="I3:I9" si="0">COUNTIF(H3:H10, "Absent")</f>
-        <v>2</v>
+        <f t="shared" ref="I3:I9" si="0">COUNTIFS($A$2:$A$100, A3, $H$2:$H$100, "Absent")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="I4">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="I5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="I6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -2997,7 +2997,7 @@
       </c>
       <c r="I7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
